--- a/docs/downloads/04/tbl_cm_educ_sex_marovoay_ampijoroa.xlsx
+++ b/docs/downloads/04/tbl_cm_educ_sex_marovoay_ampijoroa.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -463,14 +463,8 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle</t>
-        </is>
-      </c>
-      <c r="D5">
-        <v>2</v>
-      </c>
-      <c r="E5">
-        <v>6.7</v>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -555,37 +549,37 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="D9">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E9">
-        <v>10.6</v>
+        <v>12.4</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Marovoay - Tous</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Universitaire</t>
+          <t>Inconnu</t>
         </is>
       </c>
       <c r="D10">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="E10">
-        <v>1.8</v>
+        <v>11.4</v>
       </c>
     </row>
     <row r="11">
@@ -601,14 +595,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="D11">
-        <v>13</v>
+        <v>70</v>
       </c>
       <c r="E11">
-        <v>11.4</v>
+        <v>61.4</v>
       </c>
     </row>
     <row r="12">
@@ -624,14 +618,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Primaire</t>
+          <t>Secondaire 1er cycle</t>
         </is>
       </c>
       <c r="D12">
-        <v>70</v>
+        <v>26</v>
       </c>
       <c r="E12">
-        <v>61.4</v>
+        <v>22.8</v>
       </c>
     </row>
     <row r="13">
@@ -647,14 +641,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="D13">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="E13">
-        <v>22.8</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="14">
@@ -665,19 +659,19 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle</t>
+          <t>Inconnu</t>
         </is>
       </c>
       <c r="D14">
-        <v>5</v>
+        <v>65</v>
       </c>
       <c r="E14">
-        <v>4.4</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15">
@@ -693,14 +687,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="D15">
-        <v>67</v>
+        <v>199</v>
       </c>
       <c r="E15">
-        <v>16.5</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="16">
@@ -716,14 +710,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Primaire</t>
+          <t>Secondaire 1er cycle</t>
         </is>
       </c>
       <c r="D16">
-        <v>199</v>
+        <v>104</v>
       </c>
       <c r="E16">
-        <v>49.1</v>
+        <v>25.7</v>
       </c>
     </row>
     <row r="17">
@@ -739,60 +733,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="D17">
-        <v>104</v>
+        <v>37</v>
       </c>
       <c r="E17">
-        <v>25.7</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Marovoay - Tous</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Homme</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Secondaire 2ème cycle</t>
-        </is>
-      </c>
-      <c r="D18">
-        <v>33</v>
-      </c>
-      <c r="E18">
-        <v>8.1</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Marovoay - Tous</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Homme</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Universitaire</t>
-        </is>
-      </c>
-      <c r="D19">
-        <v>2</v>
-      </c>
-      <c r="E19">
-        <v>0.5</v>
+        <v>9.1</v>
       </c>
     </row>
   </sheetData>

--- a/docs/downloads/04/tbl_cm_educ_sex_marovoay_ampijoroa.xlsx
+++ b/docs/downloads/04/tbl_cm_educ_sex_marovoay_ampijoroa.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -394,7 +394,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Non scolarisé</t>
         </is>
       </c>
       <c r="D2">
@@ -483,12 +483,6 @@
           <t>Inconnu</t>
         </is>
       </c>
-      <c r="D6">
-        <v>17</v>
-      </c>
-      <c r="E6">
-        <v>15</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -503,14 +497,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Primaire</t>
+          <t>Non scolarisé</t>
         </is>
       </c>
       <c r="D7">
-        <v>51</v>
+        <v>16</v>
       </c>
       <c r="E7">
-        <v>45.1</v>
+        <v>14.2</v>
       </c>
     </row>
     <row r="8">
@@ -526,14 +520,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="D8">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="E8">
-        <v>27.4</v>
+        <v>45.1</v>
       </c>
     </row>
     <row r="9">
@@ -549,37 +543,37 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle &amp; sup.</t>
+          <t>Secondaire 1er cycle</t>
         </is>
       </c>
       <c r="D9">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="E9">
-        <v>12.4</v>
+        <v>27.4</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Marovoay - Ampijoroa</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="D10">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E10">
-        <v>11.4</v>
+        <v>12.4</v>
       </c>
     </row>
     <row r="11">
@@ -595,14 +589,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Primaire</t>
+          <t>Non scolarisé</t>
         </is>
       </c>
       <c r="D11">
-        <v>70</v>
+        <v>13</v>
       </c>
       <c r="E11">
-        <v>61.4</v>
+        <v>11.4</v>
       </c>
     </row>
     <row r="12">
@@ -618,14 +612,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="D12">
-        <v>26</v>
+        <v>70</v>
       </c>
       <c r="E12">
-        <v>22.8</v>
+        <v>61.4</v>
       </c>
     </row>
     <row r="13">
@@ -641,14 +635,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle &amp; sup.</t>
+          <t>Secondaire 1er cycle</t>
         </is>
       </c>
       <c r="D13">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="E13">
-        <v>4.4</v>
+        <v>22.8</v>
       </c>
     </row>
     <row r="14">
@@ -659,19 +653,19 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="D14">
-        <v>65</v>
+        <v>5</v>
       </c>
       <c r="E14">
-        <v>16</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="15">
@@ -687,14 +681,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Primaire</t>
+          <t>Inconnu</t>
         </is>
       </c>
       <c r="D15">
-        <v>199</v>
+        <v>6</v>
       </c>
       <c r="E15">
-        <v>49.1</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="16">
@@ -710,14 +704,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
+          <t>Non scolarisé</t>
         </is>
       </c>
       <c r="D16">
-        <v>104</v>
+        <v>59</v>
       </c>
       <c r="E16">
-        <v>25.7</v>
+        <v>14.6</v>
       </c>
     </row>
     <row r="17">
@@ -733,13 +727,59 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
+          <t>Primaire</t>
+        </is>
+      </c>
+      <c r="D17">
+        <v>199</v>
+      </c>
+      <c r="E17">
+        <v>49.1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Marovoay - Tous</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Homme</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Secondaire 1er cycle</t>
+        </is>
+      </c>
+      <c r="D18">
+        <v>104</v>
+      </c>
+      <c r="E18">
+        <v>25.7</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Marovoay - Tous</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Homme</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
           <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
-      <c r="D17">
+      <c r="D19">
         <v>37</v>
       </c>
-      <c r="E17">
+      <c r="E19">
         <v>9.1</v>
       </c>
     </row>
